--- a/jeaf-generator-messages/src/main/resources/JEAFGeneratorMessages.xlsx
+++ b/jeaf-generator-messages/src/main/resources/JEAFGeneratorMessages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator-messages/jeaf-generator-messages/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362955EA-C81A-0D41-9294-4B65258ED4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AED2775-A3EE-8A44-AAB7-273CE6D7A527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="600" windowWidth="25260" windowHeight="28200" activeTab="2" xr2:uid="{ADB42BFB-6EC0-410A-8CB1-9C298A092AA4}"/>
+    <workbookView xWindow="1240" yWindow="680" windowWidth="33320" windowHeight="21660" activeTab="2" xr2:uid="{ADB42BFB-6EC0-410A-8CB1-9C298A092AA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Class-Info" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="330">
   <si>
     <t>Class-Info</t>
   </si>
@@ -1236,6 +1236,51 @@
   </si>
   <si>
     <t>Operation ''{0}(…)'' has optional parameter ''{1}'' that uses a primitive type. Due to an explicitly enabled check in your Maven configuration it is required that there is an explicit default value for all optional primitive parameters.</t>
+  </si>
+  <si>
+    <t>INVALID_SOURCE_OR_TARGET_FOR_MVN_DEPENDENCY</t>
+  </si>
+  <si>
+    <t>JEAF Generator supports to define depenencies between elements. As this information is used to generate Maven POM files source and target of such dependencies must be elements with stereotype «MavenProject».</t>
+  </si>
+  <si>
+    <t>Dependencies with stereotype «MavenDependency», «MavenProjectDependency» and «MavenParentPOM» are only valid between elements with stereotype «MavenProject». Source ''{0}'' and / or target ''{1}'' does not match to this copnstraint.</t>
+  </si>
+  <si>
+    <t>NO_MODEL_COORDINATES_IN_PARENT</t>
+  </si>
+  <si>
+    <t>JEAF Generator supports to use UML model coordinates from parent POM (direct or indirect). However there the coordinates of the UML model have to be defined.</t>
+  </si>
+  <si>
+    <t>Parent project(s) of Maven project ''{0}'' do not define coordinates for the location of the UML model. However this is expected for this Maven project. Please fix Maven plugin configuration or UML model.</t>
+  </si>
+  <si>
+    <t>TARGET_PROJECT_HAS_WRONG_ARCHETYPE</t>
+  </si>
+  <si>
+    <t>Stereotype «MavenDependency» can only be used if the target Maven project is of archetype "ARTIFACT". Please fix the dependency from ''{0}'' to ''{1}''.</t>
+  </si>
+  <si>
+    <t>Stereotype «MavenDependency» can only be used if the target Maven project is of archetype "ARTIFACT".</t>
+  </si>
+  <si>
+    <t>SERVICE_TYPES_ONLY_APPLICABLE_FOR_SERVICE_MODELS</t>
+  </si>
+  <si>
+    <t>Tag "serviceTypes" is only applicable for Maven projects with archetype "SERVICE_MODEL".</t>
+  </si>
+  <si>
+    <t>Tag "serviceTypes" is only applicable for Maven projects with archetype "SERVICE_MODEL". Please fix UML model element ''{0}''.</t>
+  </si>
+  <si>
+    <t>ARCHETYPE_DO_NOT_MATCH_TO_DEPNDENCY_TYPE</t>
+  </si>
+  <si>
+    <t>When there is a Maven project dependency in the UML model then the so called module dependency type must match to the projects archetype.</t>
+  </si>
+  <si>
+    <t>Module dependency type ''{0}'' does not match to archetype of source ''{1}'' and target ''{2}''.</t>
   </si>
 </sst>
 </file>
@@ -1538,34 +1583,34 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C78FBD0B-2020-4712-86AE-D7BCE8E6B516}" name="Tabelle145" displayName="Tabelle145" ref="A1:I101" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C78FBD0B-2020-4712-86AE-D7BCE8E6B516}" name="Tabelle145" displayName="Tabelle145" ref="A1:I101" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{7537072B-DA19-4318-B7AA-14135B307274}" name="Message-ID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{F323142C-244E-41F1-93A6-0AA08BE7B8FF}" name="Name" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{AF060E36-B6B7-4892-8622-D50FCC5AE8CD}" name="Message-Type" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{0654D6ED-D6B6-4967-8B32-955A11DEDA63}" name="Trace-Level" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{ED3A71A8-CA63-40A0-BEDA-3FDF4E2F8316}" name="Deprecated" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{22FBD96D-7809-44EA-9E67-2F10C6A009AE}" name="Description" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{E825B3A2-5DED-420D-AB44-AB28640EE14E}" name="Default-Text" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{9FDD04FF-3345-4296-824C-3195B380304A}" name="de" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{5A1A78E9-A7C9-4DAD-9525-03A8700CD71F}" name="de_CH" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{7537072B-DA19-4318-B7AA-14135B307274}" name="Message-ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{F323142C-244E-41F1-93A6-0AA08BE7B8FF}" name="Name" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{AF060E36-B6B7-4892-8622-D50FCC5AE8CD}" name="Message-Type" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{0654D6ED-D6B6-4967-8B32-955A11DEDA63}" name="Trace-Level" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{ED3A71A8-CA63-40A0-BEDA-3FDF4E2F8316}" name="Deprecated" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{22FBD96D-7809-44EA-9E67-2F10C6A009AE}" name="Description" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{E825B3A2-5DED-420D-AB44-AB28640EE14E}" name="Default-Text" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{9FDD04FF-3345-4296-824C-3195B380304A}" name="de" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{5A1A78E9-A7C9-4DAD-9525-03A8700CD71F}" name="de_CH" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{948296A2-6F04-4C20-9E8E-5BB5FABA5A70}" name="Tabelle14" displayName="Tabelle14" ref="A1:I101" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{948296A2-6F04-4C20-9E8E-5BB5FABA5A70}" name="Tabelle14" displayName="Tabelle14" ref="A1:I101" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{967D6801-B5F2-4970-A27A-F85C37854D60}" name="Message-ID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{88E5ADDA-3853-468E-B030-85021C9A6650}" name="Name" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{740749F7-6FAA-4481-BC95-7F1796A2432D}" name="Message-Type" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{19311204-5730-4A79-9D38-7FC86468DF77}" name="Trace-Level" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{3E8ADF41-0BB1-4927-B4B6-18C125FBAB4D}" name="Deprecated" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{6165C651-89C2-47C8-9C0A-7E31E39C3BDC}" name="Description" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{C07594BE-26A2-446A-9EEB-CCB78235D1A1}" name="Default-Text" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{B4B20E49-AADE-4F41-BEBA-FA3CF75FE9C4}" name="de" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{996AA4AD-7F15-4AE4-AF3A-25B3F210F094}" name="de_CH" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{967D6801-B5F2-4970-A27A-F85C37854D60}" name="Message-ID" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{88E5ADDA-3853-468E-B030-85021C9A6650}" name="Name" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{740749F7-6FAA-4481-BC95-7F1796A2432D}" name="Message-Type" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{19311204-5730-4A79-9D38-7FC86468DF77}" name="Trace-Level" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{3E8ADF41-0BB1-4927-B4B6-18C125FBAB4D}" name="Deprecated" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{6165C651-89C2-47C8-9C0A-7E31E39C3BDC}" name="Description" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{C07594BE-26A2-446A-9EEB-CCB78235D1A1}" name="Default-Text" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{B4B20E49-AADE-4F41-BEBA-FA3CF75FE9C4}" name="de" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{996AA4AD-7F15-4AE4-AF3A-25B3F210F094}" name="de_CH" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4405,29 +4450,104 @@
         <v>314</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" ht="64" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>9181</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>9182</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B84" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>9183</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B85" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>9184</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B86" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>9185</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">

--- a/jeaf-generator-messages/src/main/resources/JEAFGeneratorMessages.xlsx
+++ b/jeaf-generator-messages/src/main/resources/JEAFGeneratorMessages.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator-messages/jeaf-generator-messages/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5270039F-D62B-A04C-B74F-4AB91CF1DBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFCF081-8A51-8044-B76C-7D6F7BAE686F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25620" yWindow="640" windowWidth="51160" windowHeight="28140" activeTab="2" xr2:uid="{ADB42BFB-6EC0-410A-8CB1-9C298A092AA4}"/>
   </bookViews>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="336">
   <si>
     <t>Class-Info</t>
   </si>
@@ -1290,6 +1290,16 @@
   </si>
   <si>
     <t>When working with bean parameters, it is generally expected that every property of a bean parameter class represents a header, path, query, or cookie parameter. In cases where a bean parameter class also includes simple properties for other purposes, those properties must be explicitly marked as “not a REST parameter” using stereotype «NoRESTParam».</t>
+  </si>
+  <si>
+    <t>TOO_MANY_COMPATIBILITY_INFOS</t>
+  </si>
+  <si>
+    <t>So called compatibility groups can be used to simplify handling of deprecation and breaking changes message. One part of this is defining compatibility info for a compatibility group.
+However you can not define more the one compatibility info for a compatibility group</t>
+  </si>
+  <si>
+    <t>«CompatibilityGroup» ''{0}'' has multiple «CompatibilityInfo» definitions associated ({1}). Please make sure that there is not more than one.</t>
   </si>
 </sst>
 </file>
@@ -4579,9 +4589,24 @@
         <v>331</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>9187</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
@@ -4645,7 +4670,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A101" xr:uid="{AACEF8C0-EC92-4686-A8C3-E4036D94D483}">
       <formula1>0</formula1>
     </dataValidation>
@@ -4658,7 +4683,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EA474BAA-D9F0-48C4-BFC6-D7532DADFCD0}">
           <x14:formula1>
             <xm:f>'Predefined-Values'!$C$4:$C$5</xm:f>
